--- a/data/trans_bre/IP19C09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,0</t>
+          <t>-8,18; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 1,3</t>
+          <t>-11,05; 1,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,7</t>
+          <t>0,0; 11,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,27</t>
+          <t>-4,31; 0,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,53</t>
+          <t>-1,49; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,0</t>
+          <t>-1,53; 2,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-88,2; 33,29</t>
+          <t>-86,38; 29,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 362,38</t>
+          <t>-70,67; 516,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,51; 423,21</t>
+          <t>-66,99; 337,1</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,67</t>
+          <t>-4,37; 3,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,03</t>
+          <t>-3,45; 1,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 3,15</t>
+          <t>-6,77; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-88,38; 171,2</t>
+          <t>-86,77; 272,6</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,02</t>
+          <t>-3,46; 0,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,45</t>
+          <t>-1,89; 1,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,12</t>
+          <t>-1,87; 2,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,86; 9,42</t>
+          <t>-82,53; 23,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 181,96</t>
+          <t>-71,67; 146,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 132,93</t>
+          <t>-55,8; 140,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,0</t>
+          <t>-8,43; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 1,32</t>
+          <t>-12,26; 1,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,48</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,15</t>
+          <t>-4,44; 0,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,7</t>
+          <t>-1,46; 2,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,69</t>
+          <t>-1,46; 2,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,38; 29,65</t>
+          <t>-86,47; 48,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,67; 516,87</t>
+          <t>-75,79; 426,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 337,1</t>
+          <t>-60,68; 424,53</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,68</t>
+          <t>-4,43; 3,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,99</t>
+          <t>-3,39; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 3,88</t>
+          <t>-7,19; 3,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-86,77; 272,6</t>
+          <t>-89,57; 224,52</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,11</t>
+          <t>-3,56; 0,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,44</t>
+          <t>-1,91; 1,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,01</t>
+          <t>-1,69; 2,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 23,01</t>
+          <t>-85,52; 16,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,67; 146,77</t>
+          <t>-70,99; 159,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 140,39</t>
+          <t>-54,12; 165,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 0,0</t>
+          <t>-6,97; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 1,33</t>
+          <t>-12,87; 1,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,76</t>
+          <t>0,0; 11,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,22</t>
+          <t>-4,39; 0,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,71</t>
+          <t>-1,31; 2,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,83</t>
+          <t>-1,47; 3,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,47; 48,11</t>
+          <t>-88,2; 33,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 426,99</t>
+          <t>-71,39; 362,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 424,53</t>
+          <t>-65,51; 423,21</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,4</t>
+          <t>-5,14; 3,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,98</t>
+          <t>-3,26; 2,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 3,31</t>
+          <t>-7,82; 3,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-89,57; 224,52</t>
+          <t>-88,38; 171,2</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,19</t>
+          <t>-3,62; 0,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,53</t>
+          <t>-1,81; 1,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,15</t>
+          <t>-1,86; 2,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,52; 16,02</t>
+          <t>-83,86; 9,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,99; 159,07</t>
+          <t>-69,87; 181,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 165,96</t>
+          <t>-58,11; 132,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,7</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-67,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-1.406425072020193</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.697173887677912</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.612627370636365</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.6736053241519337</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +628,128 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,97; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-12,87; 1,3</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,7</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.967253813628625</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-12.8710129712115</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.295960112058421</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.69688009763606</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-56,24%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>31,07%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,39; 0,27</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,31; 2,53</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,47; 3,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-88,2; 33,29</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-71,39; 362,38</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-65,51; 423,21</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.964949141761924</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4656418908334681</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.454694720309751</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.5624428717093519</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3106901896278289</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2628531401215609</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-28,74%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-42,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-30,38%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.390172399918376</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.310179585553958</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.469362263416646</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.8820141408709534</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.713892443524802</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6550804710860223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,14; 3,67</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,26; 2,03</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,82; 3,15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-88,38; 171,2</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2719016099267243</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.528430764486694</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.00145798024973</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.3329114600861824</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3.623790882693783</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.23207191676878</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +757,153 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-54,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,63%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.747585897550846</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.6872071586192892</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.555009810204146</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.2874310116283968</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4250746927283394</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3038499690153928</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 0,02</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 1,45</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 2,12</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-83,86; 9,42</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-69,87; 181,96</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-58,11; 132,93</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.141090098709071</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.264019778643284</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.824155810474978</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.8837808136528302</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.674010403505866</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.02982655885283</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.153722008314605</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>1.711992509134933</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.671419679464448</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1938696565544074</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1283082115822249</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.545203008732238</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1062768404491198</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.05305336910917367</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.617815544654816</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.808478617752896</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.858607911069198</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8385625379426065</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6986507045858715</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5810627472797583</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.01866911455452469</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.446720939344781</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.122949803087668</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.09421649981187356</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.819562085037443</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.32929966705838</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +912,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
